--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11226,22 +11226,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11300,12 +11300,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,29 +11379,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11332,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11364,12 +11364,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,29 +11475,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11268,12 +11268,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11327,17 +11327,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,29 +11475,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,29 +11443,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11684,12 +11684,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11300,12 +11300,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,29 +11443,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11620,12 +11620,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11268,12 +11268,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,29 +11315,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,29 +11475,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳牡丹大道销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
+          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车洛阳牡丹大道销售中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号，东方红 704青创产业园</t>
+          <t>河南省洛阳市洛龙区牡丹大道与杜预街交叉路口西200米路北新能源汽车城内</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,29 +11251,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11300,12 +11300,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11332,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,29 +11347,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,29 +11475,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11748,12 +11748,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11258,22 +11258,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11332,12 +11332,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11347,29 +11347,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,29 +11507,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698 号一层-2 → 杭州市西湖区西溪路698号一层-2</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11780,12 +11780,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州元泽尚奥用户中心</t>
+          <t>兰州盛通奥达汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
+          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>兰州盛通奥达汽车销售服务有限公司</t>
+          <t>上汽奥迪兰州尚奥用户中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市城关区焦家湾街道焦家湾南路 105 号（三角花园向东2公里）</t>
+          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州尚奥用户中心</t>
+          <t>上汽奥迪兰州元泽尚奥用户中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区沙井驿街道北滨河西路1757号第1层西侧展厅</t>
+          <t>甘肃省兰州市安宁区孔家崖街道北滨河西路666附4号</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11295,17 +11295,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11364,12 +11364,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11391,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,29 +11507,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11551,17 +11551,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11588,12 +11588,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11684,12 +11684,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>南宁江南保时捷中心</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>南宁保时捷中心</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11898,22 +11898,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11994,22 +11994,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>南宁江南保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>南宁保时捷中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12026,22 +12026,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260706_vs_20260713.xlsx
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市昌平瑶光路服务中心</t>
+          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>瑶光路8号</t>
+          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市顺义区潮白河公园服务中心</t>
+          <t>小米汽车北京市昌平瑶光路服务中心</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>北京市顺义区南彩镇祥东路11号曲美新能源小镇内</t>
+          <t>瑶光路8号</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
+          <t>小鹏汽车武汉黄浦科技园销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
+          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11283,29 +11283,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
+          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛银川西路销售服务中心</t>
+          <t>上海益申</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
+          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波江北销售服务中心</t>
+          <t>小鹏汽车青岛银川西路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
+          <t>山东青岛市南区银川西路21号 → 山东省青岛市南区银川西路21号</t>
         </is>
       </c>
     </row>
@@ -11396,12 +11396,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车江门蓬江销售服务中心</t>
+          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
+          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11423,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
+          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
         </is>
       </c>
     </row>
@@ -11455,17 +11455,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车衢州浙西汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市盐都区新都路88号 → 江苏省盐城市新都路88号</t>
+          <t>浙江省衢州市柯城区浙西大道109号16区1幢 → 浙江省衢州市柯城区浙西大道109号16区1栋</t>
         </is>
       </c>
     </row>
@@ -11492,12 +11492,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11507,29 +11507,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
+          <t>浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1 → 浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海益申</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1358、1386、1388号 → 上海市青浦区华新镇华腾路9559、9595号3栋、4栋、5栋</t>
+          <t>浙江省温州市经济技术开发区高一路178号 → 浙江省温州市龙湾区高一路178号小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
+          <t>小鹏汽车台州路桥服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
+          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙岗信义汽车城销售服务中心</t>
+          <t>小鹏汽车温州瓯海国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A → 广东省深圳市龙岗区园山街道银荷社区银盛路33号信义汽车城39A、39B栋展位39A</t>
+          <t>浙江省温州市瓯海区永庆街瓯融汽车产业园1号 → 浙江省温州市瓯海区娄桥街道永庆街瓯融汽车产业园1号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南昌青山湖销售服务中心</t>
+          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
+          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 龙岩龙门</t>
+          <t>小鹏汽车宁波江北销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
+          <t>浙江省宁波市江北区中官新路555号18#-1 → 浙江宁波江北区中官新路555号5号-1 宁波小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车台州路桥服务中心</t>
+          <t>小鹏汽车江门蓬江销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省台州市路桥区新安南街766号 → 浙江省台州市路桥区新安南街760号</t>
+          <t>江门市蓬江区建设三路215号3栋首层 → 广东省江门市蓬江区建设三路215号3栋首层</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车余姚东部汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省余姚市凤山街道同光村余丈路2号（319省道） → 浙江省宁波市余姚市凤山街道同光村东江汽车城8号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉黄浦科技园销售中心</t>
+          <t>蔚来体验中心 | 龙岩龙门</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江岸区石桥一路10号 → 江岸区黄浦科技园特6号</t>
+          <t>福建省龙岩市新罗区龙门镇物流大道333-13号 → 福建省龙岩市新罗区物流大道213号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车菏泽汽车小镇销售服务中心</t>
+          <t>小鹏汽车南昌青山湖销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山东省菏泽市定陶区汽车小镇东门向北300米 → 山东省菏泽市定陶区广州路与曙光路交叉口向东50米路北</t>
+          <t>南昌市青山湖区京东南大道366号 → 江西省南昌市青山湖区京东南大道366号</t>
         </is>
       </c>
     </row>
@@ -11834,22 +11834,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰4S中心</t>
+          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>太原沃之杰卫星店</t>
+          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -11866,22 +11866,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作解放区焦作万达</t>
+          <t>温州国鼎4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省焦作市解放区焦作万达</t>
+          <t>温州国鼎维修中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞卫星店</t>
+          <t>太原沃之杰4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>太原沃之瑞4S中心</t>
+          <t>太原沃之杰卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -11930,22 +11930,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎4S中心</t>
+          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>温州国鼎维修中心</t>
+          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -11962,22 +11962,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之瑞卫星店</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市塘厦镇塘厦天虹</t>
+          <t>太原沃之瑞4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区郑州正弘汇汽车体验店</t>
+          <t>小米汽车河南焦作解放区焦作万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家河南省郑州市高新区正弘汇汽车体验店</t>
+          <t>小米汽车河南省焦作市解放区焦作万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
